--- a/Deliverables/sprint-02/planning-documents.xlsx
+++ b/Deliverables/sprint-02/planning-documents.xlsx
@@ -272,22 +272,22 @@
     <t>Andrew Ebied</t>
   </si>
   <si>
+    <t>Hasnat Ahmed</t>
+  </si>
+  <si>
+    <t>Hossam Amer</t>
+  </si>
+  <si>
+    <t>Muhamad Zeeshan</t>
+  </si>
+  <si>
+    <t>Abdul Haseeb</t>
+  </si>
+  <si>
+    <t>Marcel Vogt</t>
+  </si>
+  <si>
     <t>Hannes Vinzens</t>
-  </si>
-  <si>
-    <t>Hasnat Ahmed</t>
-  </si>
-  <si>
-    <t>Hossam Amer</t>
-  </si>
-  <si>
-    <t>Muhamad Zeeshan</t>
-  </si>
-  <si>
-    <t>Abdul Haseeb</t>
-  </si>
-  <si>
-    <t>Marcel Vogt</t>
   </si>
   <si>
     <t>/</t>
@@ -3147,7 +3147,7 @@
         <v>78</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>80</v>
@@ -3172,7 +3172,7 @@
         <v>78</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>80</v>
@@ -3197,7 +3197,7 @@
         <v>78</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>80</v>
@@ -3222,7 +3222,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>80</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>80</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>80</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>80</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>80</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>80</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>80</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>80</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>80</v>
@@ -3816,7 +3816,7 @@
         <v>141</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
@@ -3824,7 +3824,7 @@
         <v>141</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56">
@@ -3832,7 +3832,7 @@
         <v>141</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">
@@ -3848,7 +3848,7 @@
         <v>141</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59">
@@ -3864,7 +3864,7 @@
         <v>141</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
